--- a/cat_dua/upload/temp/format_import_siswa.xlsx
+++ b/cat_dua/upload/temp/format_import_siswa.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fitria\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0097E019-C81E-4FA3-A95D-E766678EE482}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C459A201-0CD1-4F8D-935E-E51970DEE973}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-2070" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
   <si>
     <t>nama</t>
   </si>
@@ -34,91 +34,49 @@
     <t>format_download_verified_ok</t>
   </si>
   <si>
-    <t>15Feb2021 Ujian Ners NonPNS</t>
-  </si>
-  <si>
-    <t>1302087110950001</t>
-  </si>
-  <si>
-    <t>3209282504920005</t>
-  </si>
-  <si>
-    <t>8104010608970002</t>
-  </si>
-  <si>
-    <t>6474022404940004</t>
-  </si>
-  <si>
-    <t>3173015803920004</t>
-  </si>
-  <si>
-    <t>3505171005910002</t>
-  </si>
-  <si>
-    <t>3174094406950002</t>
-  </si>
-  <si>
-    <t>3301236712910002</t>
-  </si>
-  <si>
-    <t>3524200604920001</t>
-  </si>
-  <si>
-    <t>3215135604960002</t>
-  </si>
-  <si>
-    <t>1709055703950001</t>
-  </si>
-  <si>
-    <t>3172066304910001</t>
-  </si>
-  <si>
-    <t>3174056510921001</t>
-  </si>
-  <si>
-    <t>3174095709910009</t>
-  </si>
-  <si>
-    <t>Elda oktavia</t>
-  </si>
-  <si>
-    <t>Veri Sugandi</t>
-  </si>
-  <si>
-    <t>Rian Andito Fesanrey</t>
-  </si>
-  <si>
-    <t>yosep fransiskus riki dosi</t>
-  </si>
-  <si>
-    <t>Norma Anggelina</t>
-  </si>
-  <si>
-    <t>Johan Syarifudin</t>
-  </si>
-  <si>
-    <t>Ns. Yuni Triwardani. S.Kep</t>
-  </si>
-  <si>
-    <t>Dwi Kristiani</t>
-  </si>
-  <si>
-    <t>Andika pitro herianto</t>
-  </si>
-  <si>
-    <t>IZDIA AFRANADA</t>
-  </si>
-  <si>
-    <t>Suntika Mawarni</t>
-  </si>
-  <si>
-    <t>Deby Mutiara Utami</t>
-  </si>
-  <si>
-    <t>Ns. Susi Erawati,S.Kep</t>
-  </si>
-  <si>
-    <t>Dina Santiara</t>
+    <t>1310044401950002</t>
+  </si>
+  <si>
+    <t>1171010808940002</t>
+  </si>
+  <si>
+    <t>3275034512940008</t>
+  </si>
+  <si>
+    <t>3672052206960002</t>
+  </si>
+  <si>
+    <t>1271024104950006</t>
+  </si>
+  <si>
+    <t>3275014810960012</t>
+  </si>
+  <si>
+    <t>3175025705940006</t>
+  </si>
+  <si>
+    <t>Diga Ana Rusfi</t>
+  </si>
+  <si>
+    <t>Hendra Dwitanto</t>
+  </si>
+  <si>
+    <t>Nina Amelinda</t>
+  </si>
+  <si>
+    <t>dr. Adrian Prasetya</t>
+  </si>
+  <si>
+    <t>dr. Agnes Chyntia Silaban</t>
+  </si>
+  <si>
+    <t>dr. Nabila Nitha Alifia</t>
+  </si>
+  <si>
+    <t>dr. Rafhanni Fayadh</t>
+  </si>
+  <si>
+    <t>20210223 Tes Uji Kompetensi Pegawai NON PNS</t>
   </si>
 </sst>
 </file>
@@ -496,12 +454,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.42578125" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.140625" customWidth="1"/>
     <col min="4" max="16384" width="9.140625" hidden="1"/>
   </cols>
   <sheetData>
@@ -523,159 +481,119 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" t="s">
-        <v>4</v>
-      </c>
+      <c r="A10" s="1"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" t="s">
-        <v>4</v>
-      </c>
+      <c r="A11" s="1"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" t="s">
-        <v>4</v>
-      </c>
+      <c r="A12" s="1"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" t="s">
-        <v>4</v>
-      </c>
+      <c r="A13" s="1"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" t="s">
-        <v>4</v>
-      </c>
+      <c r="A14" s="1"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" t="s">
-        <v>4</v>
-      </c>
+      <c r="A15" s="1"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" t="s">
-        <v>4</v>
-      </c>
+      <c r="A16" s="1"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
--- a/cat_dua/upload/temp/format_import_siswa.xlsx
+++ b/cat_dua/upload/temp/format_import_siswa.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="23628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24729"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fitria\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Download\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C459A201-0CD1-4F8D-935E-E51970DEE973}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9063FBB-8C5E-49E5-9EA1-E456C17AC764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,11 +16,20 @@
     <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="71">
   <si>
     <t>nama</t>
   </si>
@@ -34,49 +43,205 @@
     <t>format_download_verified_ok</t>
   </si>
   <si>
-    <t>1310044401950002</t>
-  </si>
-  <si>
-    <t>1171010808940002</t>
-  </si>
-  <si>
-    <t>3275034512940008</t>
-  </si>
-  <si>
-    <t>3672052206960002</t>
-  </si>
-  <si>
-    <t>1271024104950006</t>
-  </si>
-  <si>
-    <t>3275014810960012</t>
-  </si>
-  <si>
-    <t>3175025705940006</t>
-  </si>
-  <si>
-    <t>Diga Ana Rusfi</t>
-  </si>
-  <si>
-    <t>Hendra Dwitanto</t>
-  </si>
-  <si>
-    <t>Nina Amelinda</t>
-  </si>
-  <si>
-    <t>dr. Adrian Prasetya</t>
-  </si>
-  <si>
-    <t>dr. Agnes Chyntia Silaban</t>
-  </si>
-  <si>
-    <t>dr. Nabila Nitha Alifia</t>
-  </si>
-  <si>
-    <t>dr. Rafhanni Fayadh</t>
-  </si>
-  <si>
-    <t>20210223 Tes Uji Kompetensi Pegawai NON PNS</t>
+    <t>20220124 Test Potensi Akademik</t>
+  </si>
+  <si>
+    <t>Faisal Abdullah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yogi Prasetyo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setyo Aji </t>
+  </si>
+  <si>
+    <t>Ilham Khasani</t>
+  </si>
+  <si>
+    <t>Matarefo Warin, Amd. Kep</t>
+  </si>
+  <si>
+    <t>Bernadus</t>
+  </si>
+  <si>
+    <t>Ichwan Wahyu Widyantoro</t>
+  </si>
+  <si>
+    <t>Ronggo Satya Handoko</t>
+  </si>
+  <si>
+    <t>Fathur Rohman</t>
+  </si>
+  <si>
+    <t>Beni Perdana Putra</t>
+  </si>
+  <si>
+    <t>Dino Fathullah</t>
+  </si>
+  <si>
+    <t>David Marko Ryan</t>
+  </si>
+  <si>
+    <t>Aprizul Aditya</t>
+  </si>
+  <si>
+    <t>Henry Hermawan</t>
+  </si>
+  <si>
+    <t>Purwandi</t>
+  </si>
+  <si>
+    <t>Muhammad Rafi</t>
+  </si>
+  <si>
+    <t>Edward Sebastian</t>
+  </si>
+  <si>
+    <t>Rizki Rahmatullah</t>
+  </si>
+  <si>
+    <t>Alexs Pahala Abadi Siregar</t>
+  </si>
+  <si>
+    <t>Wanda Yuliandi</t>
+  </si>
+  <si>
+    <t>Albert Alapaz Samosir</t>
+  </si>
+  <si>
+    <t>Muhammad Hafidz Akbar</t>
+  </si>
+  <si>
+    <t>Muhamad Ali</t>
+  </si>
+  <si>
+    <t>M.Yazid Muzayin</t>
+  </si>
+  <si>
+    <t>Irmansyah</t>
+  </si>
+  <si>
+    <t>Indah Ratna Sari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anis Fitriani </t>
+  </si>
+  <si>
+    <t>Yulia Santi</t>
+  </si>
+  <si>
+    <t>Septiani Dwi Falahah</t>
+  </si>
+  <si>
+    <t>Mailanda Redona</t>
+  </si>
+  <si>
+    <t>Novi Ismiati</t>
+  </si>
+  <si>
+    <t>Favriella Prettimilana</t>
+  </si>
+  <si>
+    <t>Rafi Faishal Amin</t>
+  </si>
+  <si>
+    <t>3603112502970003</t>
+  </si>
+  <si>
+    <t>3202011211890006</t>
+  </si>
+  <si>
+    <t>3201011908910004</t>
+  </si>
+  <si>
+    <t>3305152306970002</t>
+  </si>
+  <si>
+    <t>3328011103920006</t>
+  </si>
+  <si>
+    <t>1811012111950003</t>
+  </si>
+  <si>
+    <t>6107131507930001</t>
+  </si>
+  <si>
+    <t>3502040603930002</t>
+  </si>
+  <si>
+    <t>3323062802930001</t>
+  </si>
+  <si>
+    <t>3319052810960005</t>
+  </si>
+  <si>
+    <t>1806210803950002</t>
+  </si>
+  <si>
+    <t>3275071612970012</t>
+  </si>
+  <si>
+    <t>3175042104970002</t>
+  </si>
+  <si>
+    <t>3275021505900021</t>
+  </si>
+  <si>
+    <t>3671073103000004</t>
+  </si>
+  <si>
+    <t>3275071209920008</t>
+  </si>
+  <si>
+    <t>3604011604920768</t>
+  </si>
+  <si>
+    <t>3202112611950003</t>
+  </si>
+  <si>
+    <t>1301051906940002</t>
+  </si>
+  <si>
+    <t>3172041110011001</t>
+  </si>
+  <si>
+    <t>3603122906960001</t>
+  </si>
+  <si>
+    <t>3174100204950007</t>
+  </si>
+  <si>
+    <t>3209181502980001</t>
+  </si>
+  <si>
+    <t>3329031504880001</t>
+  </si>
+  <si>
+    <t>3171062309910002</t>
+  </si>
+  <si>
+    <t>3674066910940005</t>
+  </si>
+  <si>
+    <t>3173075807980005</t>
+  </si>
+  <si>
+    <t>3674056809980001</t>
+  </si>
+  <si>
+    <t>3173076005980005</t>
+  </si>
+  <si>
+    <t>3201195711980006</t>
+  </si>
+  <si>
+    <t>1701044602910001</t>
+  </si>
+  <si>
+    <t>3674031401990014</t>
+  </si>
+  <si>
+    <t>3173064403950002</t>
   </si>
 </sst>
 </file>
@@ -454,12 +619,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.140625" customWidth="1"/>
+    <col min="1" max="1" width="27" customWidth="1"/>
+    <col min="2" max="2" width="42" customWidth="1"/>
+    <col min="3" max="3" width="30.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9.140625" hidden="1"/>
   </cols>
   <sheetData>
@@ -481,119 +646,369 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" t="s">
         <v>17</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
+      <c r="C16" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B28" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B29" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B30" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B31" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B32" t="s">
+        <v>33</v>
+      </c>
+      <c r="C32" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B34" t="s">
+        <v>35</v>
+      </c>
+      <c r="C34" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C35" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/cat_dua/upload/temp/format_import_siswa.xlsx
+++ b/cat_dua/upload/temp/format_import_siswa.xlsx
@@ -1,37 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10912"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22325"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/muhammadrahmansaleh/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PJ SIMRS\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A2B304B-BEE6-5D46-8CA1-DEFA4923DA53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DA9D124-451E-4034-9F22-4F56AECD89BA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="14300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="37">
   <si>
     <t>nama</t>
   </si>
@@ -45,37 +34,103 @@
     <t>format_download_verified_ok</t>
   </si>
   <si>
-    <t>Achmad Noer Balkiswandi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ahmad Syaugi </t>
-  </si>
-  <si>
-    <t>Krisna Aditya</t>
-  </si>
-  <si>
-    <t>Oktaviyana Emiliyanto</t>
-  </si>
-  <si>
-    <t>Davit Petrayasa</t>
-  </si>
-  <si>
-    <t>3603011610960001</t>
-  </si>
-  <si>
-    <t>3175062507950008</t>
-  </si>
-  <si>
-    <t>3208311701970001</t>
-  </si>
-  <si>
-    <t>3175054610960001</t>
-  </si>
-  <si>
-    <t>3271061403970001</t>
-  </si>
-  <si>
-    <t>Bank Soal TPA S1</t>
+    <t>8205071609971003</t>
+  </si>
+  <si>
+    <t>3175041201031001</t>
+  </si>
+  <si>
+    <t>7605062612970001</t>
+  </si>
+  <si>
+    <t>1803073004000005</t>
+  </si>
+  <si>
+    <t>1809012405930002</t>
+  </si>
+  <si>
+    <t>3674062810000002</t>
+  </si>
+  <si>
+    <t>1807166207990001</t>
+  </si>
+  <si>
+    <t>3174102904950007</t>
+  </si>
+  <si>
+    <t>1607055309000001</t>
+  </si>
+  <si>
+    <t>3174051803950005</t>
+  </si>
+  <si>
+    <t>3671112611960003</t>
+  </si>
+  <si>
+    <t>3173016102000007</t>
+  </si>
+  <si>
+    <t>Najim Umamit Amd.TEM</t>
+  </si>
+  <si>
+    <t>Roihan Muhammad Iqbal, A.Md.T</t>
+  </si>
+  <si>
+    <t>Muhammad ilman resyah</t>
+  </si>
+  <si>
+    <t>Bernada Pramara Lufi A.Md.T</t>
+  </si>
+  <si>
+    <t>Firman Meriyanto</t>
+  </si>
+  <si>
+    <t>Muhammad Bagus Setia Ramadhan, S. Tr. T</t>
+  </si>
+  <si>
+    <t>Putra arfi shintata S.Tr.TEM</t>
+  </si>
+  <si>
+    <t>Shinta Tri Haksari, AMTE</t>
+  </si>
+  <si>
+    <t>Indah wulandari ( A.Md.T )</t>
+  </si>
+  <si>
+    <t>Tajul Husnaini Str, Em</t>
+  </si>
+  <si>
+    <t>Amanda Sri Wahyuni, Amd</t>
+  </si>
+  <si>
+    <t>Saifullah Siddiq S.Tr.TEM</t>
+  </si>
+  <si>
+    <t>Sandra Sari Amd.T S.T</t>
+  </si>
+  <si>
+    <t>Rian Tio Hidayad</t>
+  </si>
+  <si>
+    <t>Andri Ardika</t>
+  </si>
+  <si>
+    <t>Mella Febrianti</t>
+  </si>
+  <si>
+    <t>1801135606980005</t>
+  </si>
+  <si>
+    <t>3521052204940007</t>
+  </si>
+  <si>
+    <t>3173014905910010</t>
+  </si>
+  <si>
+    <t>6101110502970002</t>
+  </si>
+  <si>
+    <t>Bank Soal SKD 20mar24</t>
   </si>
 </sst>
 </file>
@@ -453,21 +508,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="42" customWidth="1"/>
-    <col min="3" max="3" width="22.1640625" customWidth="1"/>
-    <col min="16384" max="16384" width="18" customWidth="1"/>
+    <col min="3" max="3" width="22.109375" customWidth="1"/>
+    <col min="4" max="16384" width="9.109375" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -478,59 +533,180 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>9</v>
       </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s">
-        <v>14</v>
+      <c r="B16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/cat_dua/upload/temp/format_import_siswa.xlsx
+++ b/cat_dua/upload/temp/format_import_siswa.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PJ SIMRS\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DA9D124-451E-4034-9F22-4F56AECD89BA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86497D54-2A6F-4DFD-B38F-ED644EF00D97}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="105">
   <si>
     <t>nama</t>
   </si>
@@ -34,103 +34,307 @@
     <t>format_download_verified_ok</t>
   </si>
   <si>
-    <t>8205071609971003</t>
-  </si>
-  <si>
-    <t>3175041201031001</t>
-  </si>
-  <si>
-    <t>7605062612970001</t>
-  </si>
-  <si>
-    <t>1803073004000005</t>
-  </si>
-  <si>
-    <t>1809012405930002</t>
-  </si>
-  <si>
-    <t>3674062810000002</t>
-  </si>
-  <si>
-    <t>1807166207990001</t>
-  </si>
-  <si>
-    <t>3174102904950007</t>
-  </si>
-  <si>
-    <t>1607055309000001</t>
-  </si>
-  <si>
-    <t>3174051803950005</t>
-  </si>
-  <si>
-    <t>3671112611960003</t>
-  </si>
-  <si>
-    <t>3173016102000007</t>
-  </si>
-  <si>
-    <t>Najim Umamit Amd.TEM</t>
-  </si>
-  <si>
-    <t>Roihan Muhammad Iqbal, A.Md.T</t>
-  </si>
-  <si>
-    <t>Muhammad ilman resyah</t>
-  </si>
-  <si>
-    <t>Bernada Pramara Lufi A.Md.T</t>
-  </si>
-  <si>
-    <t>Firman Meriyanto</t>
-  </si>
-  <si>
-    <t>Muhammad Bagus Setia Ramadhan, S. Tr. T</t>
-  </si>
-  <si>
-    <t>Putra arfi shintata S.Tr.TEM</t>
-  </si>
-  <si>
-    <t>Shinta Tri Haksari, AMTE</t>
-  </si>
-  <si>
-    <t>Indah wulandari ( A.Md.T )</t>
-  </si>
-  <si>
-    <t>Tajul Husnaini Str, Em</t>
-  </si>
-  <si>
-    <t>Amanda Sri Wahyuni, Amd</t>
-  </si>
-  <si>
-    <t>Saifullah Siddiq S.Tr.TEM</t>
-  </si>
-  <si>
-    <t>Sandra Sari Amd.T S.T</t>
-  </si>
-  <si>
-    <t>Rian Tio Hidayad</t>
-  </si>
-  <si>
-    <t>Andri Ardika</t>
-  </si>
-  <si>
-    <t>Mella Febrianti</t>
-  </si>
-  <si>
-    <t>1801135606980005</t>
-  </si>
-  <si>
-    <t>3521052204940007</t>
-  </si>
-  <si>
-    <t>3173014905910010</t>
-  </si>
-  <si>
-    <t>6101110502970002</t>
-  </si>
-  <si>
-    <t>Bank Soal SKD 20mar24</t>
+    <t>Bank Soal Petugas Kebersihan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nita Anggi Apriani Lubis </t>
+  </si>
+  <si>
+    <t>Dwi Shandy Soegiarto</t>
+  </si>
+  <si>
+    <t>Janita</t>
+  </si>
+  <si>
+    <t>Nedi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aditya Setyawan </t>
+  </si>
+  <si>
+    <t>Fitri Ardillah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGISTA YUQI HANINA </t>
+  </si>
+  <si>
+    <t>REGI REVALDI MARESKI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yogi Setiawan </t>
+  </si>
+  <si>
+    <t>Bisma Sultan Maulana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muhammad nur faaiz </t>
+  </si>
+  <si>
+    <t>Muhammad Sidik</t>
+  </si>
+  <si>
+    <t>Saiful Noor</t>
+  </si>
+  <si>
+    <t>Eko Purwito</t>
+  </si>
+  <si>
+    <t>KURNIAWAN TODI</t>
+  </si>
+  <si>
+    <t>M.ZAINI BIN SAKDUDIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Septiani Ambarwati </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUWI OKTA WIANI </t>
+  </si>
+  <si>
+    <t>ROBIATUL ADAWIYAH</t>
+  </si>
+  <si>
+    <t>Eko Apriyanto</t>
+  </si>
+  <si>
+    <t>Addy Purwanto</t>
+  </si>
+  <si>
+    <t>Ricki Firmansyah</t>
+  </si>
+  <si>
+    <t>Reizan Fadhil Arighi</t>
+  </si>
+  <si>
+    <t>Muhammad Zulaftori</t>
+  </si>
+  <si>
+    <t>TUNGGAL WICAKSANA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faisal Fajri </t>
+  </si>
+  <si>
+    <t>wiwit pujawati</t>
+  </si>
+  <si>
+    <t>Irfan Hidayatullah</t>
+  </si>
+  <si>
+    <t>Fajar faiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahmad Riadi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAYYID HASAN AL JUFRI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESTIANA DARAH AISYAH </t>
+  </si>
+  <si>
+    <t>Riski maulana</t>
+  </si>
+  <si>
+    <t>Febrio eka putra</t>
+  </si>
+  <si>
+    <t>Ahmad tajarudin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maulid Nugraha </t>
+  </si>
+  <si>
+    <t>Miftahul hasanah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muhammad Yusuf </t>
+  </si>
+  <si>
+    <t>Muhammad faisal</t>
+  </si>
+  <si>
+    <t>Aminah nabila</t>
+  </si>
+  <si>
+    <t>Muhammad Bambang Santoso</t>
+  </si>
+  <si>
+    <t>Laksmono Adzani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADRIAN PARLINDUNGAN PABER PANJAITAN </t>
+  </si>
+  <si>
+    <t>Siti zubaedah</t>
+  </si>
+  <si>
+    <t>Tri Prasetyawan</t>
+  </si>
+  <si>
+    <t>Ade reni  aprina</t>
+  </si>
+  <si>
+    <t>Maliq abdurofiq</t>
+  </si>
+  <si>
+    <t>Arief febriansyah</t>
+  </si>
+  <si>
+    <t>muhammad fadhil anwar</t>
+  </si>
+  <si>
+    <t>Faishal Abdurrachman</t>
+  </si>
+  <si>
+    <t>3174014704951002</t>
+  </si>
+  <si>
+    <t>3173010810000002</t>
+  </si>
+  <si>
+    <t>3171074501011001</t>
+  </si>
+  <si>
+    <t>3604101105870333</t>
+  </si>
+  <si>
+    <t>3171070305980001</t>
+  </si>
+  <si>
+    <t>3174046304910002</t>
+  </si>
+  <si>
+    <t>3175046011980002</t>
+  </si>
+  <si>
+    <t>3171011307960004</t>
+  </si>
+  <si>
+    <t>3171070409981001</t>
+  </si>
+  <si>
+    <t>3173070807991002</t>
+  </si>
+  <si>
+    <t>3173011512960008</t>
+  </si>
+  <si>
+    <t>3175102406990008</t>
+  </si>
+  <si>
+    <t>3171070310960001</t>
+  </si>
+  <si>
+    <t>3174060808800007</t>
+  </si>
+  <si>
+    <t>3174051907780006</t>
+  </si>
+  <si>
+    <t>3173012209830015</t>
+  </si>
+  <si>
+    <t>3175034909000006</t>
+  </si>
+  <si>
+    <t>3175035310020003</t>
+  </si>
+  <si>
+    <t>3174065106970005</t>
+  </si>
+  <si>
+    <t>3171071704950004</t>
+  </si>
+  <si>
+    <t>3172052012850001</t>
+  </si>
+  <si>
+    <t>3203280104000006</t>
+  </si>
+  <si>
+    <t>3174050612940004</t>
+  </si>
+  <si>
+    <t>1405050410910003</t>
+  </si>
+  <si>
+    <t>3171030201031001</t>
+  </si>
+  <si>
+    <t>3175072706020009</t>
+  </si>
+  <si>
+    <t>3173025608000003</t>
+  </si>
+  <si>
+    <t>3172022310030005</t>
+  </si>
+  <si>
+    <t>3174042102970004</t>
+  </si>
+  <si>
+    <t>3175041310800013</t>
+  </si>
+  <si>
+    <t>6304052611020003</t>
+  </si>
+  <si>
+    <t>3171074906930005</t>
+  </si>
+  <si>
+    <t>3171072112960005</t>
+  </si>
+  <si>
+    <t>1304022302850001</t>
+  </si>
+  <si>
+    <t>3201120605960004</t>
+  </si>
+  <si>
+    <t>3171072504870004</t>
+  </si>
+  <si>
+    <t>3171036104990010</t>
+  </si>
+  <si>
+    <t>3173071506030005</t>
+  </si>
+  <si>
+    <t>3174083006960003</t>
+  </si>
+  <si>
+    <t>3175066408990005</t>
+  </si>
+  <si>
+    <t>3210170707040081</t>
+  </si>
+  <si>
+    <t>3175043107990005</t>
+  </si>
+  <si>
+    <t>3603111603040006</t>
+  </si>
+  <si>
+    <t>3175025111880008</t>
+  </si>
+  <si>
+    <t>3172012407940004</t>
+  </si>
+  <si>
+    <t>3175066804820020</t>
+  </si>
+  <si>
+    <t>3201032407960001</t>
+  </si>
+  <si>
+    <t>3175031902980002</t>
+  </si>
+  <si>
+    <t>3173071205030002</t>
+  </si>
+  <si>
+    <t>3171031906980005</t>
   </si>
 </sst>
 </file>
@@ -508,12 +712,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="42" customWidth="1"/>
-    <col min="3" max="3" width="22.109375" customWidth="1"/>
+    <col min="3" max="3" width="27.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9.109375" hidden="1"/>
   </cols>
   <sheetData>
@@ -534,179 +738,553 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>4</v>
+      <c r="A3" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>5</v>
+      <c r="A4" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>6</v>
+      <c r="A5" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>7</v>
+      <c r="A6" s="1" t="s">
+        <v>58</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>8</v>
+      <c r="A7" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>9</v>
+      <c r="A8" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>10</v>
+      <c r="A11" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>11</v>
+      <c r="A12" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>12</v>
+      <c r="A13" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>13</v>
+      <c r="A14" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>14</v>
+      <c r="A16" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>76</v>
+      </c>
+      <c r="B24" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>77</v>
+      </c>
+      <c r="B25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>79</v>
+      </c>
+      <c r="B27" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>80</v>
+      </c>
+      <c r="B28" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>81</v>
+      </c>
+      <c r="B29" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>82</v>
+      </c>
+      <c r="B30" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>83</v>
+      </c>
+      <c r="B31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C31" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>84</v>
+      </c>
+      <c r="B32" t="s">
+        <v>34</v>
+      </c>
+      <c r="C32" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>85</v>
+      </c>
+      <c r="B33" t="s">
         <v>35</v>
       </c>
-      <c r="B17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="C33" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>86</v>
+      </c>
+      <c r="B34" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" t="s">
-        <v>36</v>
+      <c r="C34" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>87</v>
+      </c>
+      <c r="B35" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>88</v>
+      </c>
+      <c r="B36" t="s">
+        <v>38</v>
+      </c>
+      <c r="C36" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>89</v>
+      </c>
+      <c r="B37" t="s">
+        <v>39</v>
+      </c>
+      <c r="C37" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>90</v>
+      </c>
+      <c r="B38" t="s">
+        <v>40</v>
+      </c>
+      <c r="C38" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>91</v>
+      </c>
+      <c r="B39" t="s">
+        <v>41</v>
+      </c>
+      <c r="C39" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>92</v>
+      </c>
+      <c r="B40" t="s">
+        <v>42</v>
+      </c>
+      <c r="C40" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>93</v>
+      </c>
+      <c r="B41" t="s">
+        <v>43</v>
+      </c>
+      <c r="C41" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>94</v>
+      </c>
+      <c r="B42" t="s">
+        <v>44</v>
+      </c>
+      <c r="C42" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>95</v>
+      </c>
+      <c r="B43" t="s">
+        <v>45</v>
+      </c>
+      <c r="C43" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>96</v>
+      </c>
+      <c r="B44" t="s">
+        <v>46</v>
+      </c>
+      <c r="C44" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>97</v>
+      </c>
+      <c r="B45" t="s">
+        <v>47</v>
+      </c>
+      <c r="C45" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>98</v>
+      </c>
+      <c r="B46" t="s">
+        <v>48</v>
+      </c>
+      <c r="C46" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>99</v>
+      </c>
+      <c r="B47" t="s">
+        <v>49</v>
+      </c>
+      <c r="C47" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>100</v>
+      </c>
+      <c r="B48" t="s">
+        <v>50</v>
+      </c>
+      <c r="C48" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>101</v>
+      </c>
+      <c r="B49" t="s">
+        <v>51</v>
+      </c>
+      <c r="C49" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>102</v>
+      </c>
+      <c r="B50" t="s">
+        <v>52</v>
+      </c>
+      <c r="C50" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>103</v>
+      </c>
+      <c r="B51" t="s">
+        <v>53</v>
+      </c>
+      <c r="C51" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>104</v>
+      </c>
+      <c r="B52" t="s">
+        <v>54</v>
+      </c>
+      <c r="C52" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
